--- a/Result/profitability/8083.xlsx
+++ b/Result/profitability/8083.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.5</v>
       </c>
       <c r="M2" t="n">
-        <v>2.09</v>
+        <v>2.3125</v>
       </c>
       <c r="N2" t="n">
-        <v>39.86375</v>
+        <v>40.04125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.73</v>
       </c>
       <c r="M3" t="n">
-        <v>1.9575</v>
+        <v>2.1675</v>
       </c>
       <c r="N3" t="n">
-        <v>38.195</v>
+        <v>38.5675</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.57</v>
       </c>
       <c r="M4" t="n">
-        <v>1.7925</v>
+        <v>2.0025</v>
       </c>
       <c r="N4" t="n">
-        <v>36.57</v>
+        <v>36.78875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.26</v>
       </c>
       <c r="M5" t="n">
-        <v>1.58875</v>
+        <v>1.68125</v>
       </c>
       <c r="N5" t="n">
-        <v>34.6425</v>
+        <v>34.955</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.29</v>
       </c>
       <c r="M6" t="n">
-        <v>1.27125</v>
+        <v>1.4275</v>
       </c>
       <c r="N6" t="n">
-        <v>32.89624999999999</v>
+        <v>33.5425</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.22</v>
       </c>
       <c r="M7" t="n">
-        <v>1.00875</v>
+        <v>1.11</v>
       </c>
       <c r="N7" t="n">
-        <v>31.74625</v>
+        <v>32.2325</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.44</v>
       </c>
       <c r="M8" t="n">
-        <v>0.71875</v>
+        <v>0.8225</v>
       </c>
       <c r="N8" t="n">
-        <v>30.6725</v>
+        <v>30.86625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8083</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>423</v>
+      </c>
+      <c r="D75" t="n">
+        <v>237</v>
+      </c>
+      <c r="E75" t="n">
+        <v>185</v>
+      </c>
+      <c r="F75" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="G75" t="n">
+        <v>156</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>36.90%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>157</v>
+      </c>
+      <c r="K75" t="n">
+        <v>125</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.47375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>41.4425</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.8299999999999996</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.302919708029197</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.550000000000004</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.03664302600472813</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.7399999999999998</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.2614840989399292</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.06045949214026591</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
